--- a/StructureDefinition-mii-pr-onko-prostate-gleason-score-gesamt.xlsx
+++ b/StructureDefinition-mii-pr-onko-prostate-gleason-score-gesamt.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:49:31+00:00</t>
+    <t>2026-09-14T12:58:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -889,6 +889,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -1006,6 +1009,9 @@
   </si>
   <si>
     <t>Observation.code.coding:loinc.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.code.coding:loinc.version</t>
@@ -5752,7 +5758,7 @@
         <v>82</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>82</v>
@@ -5791,7 +5797,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5815,7 +5821,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5826,10 +5832,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5855,13 +5861,13 @@
         <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5911,7 +5917,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5935,7 +5941,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5946,10 +5952,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5975,14 +5981,14 @@
         <v>168</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6031,7 +6037,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6055,7 +6061,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6066,10 +6072,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6095,14 +6101,14 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6151,7 +6157,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6175,7 +6181,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6186,10 +6192,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6212,19 +6218,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6273,7 +6279,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6297,7 +6303,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6308,13 +6314,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>82</v>
@@ -6358,7 +6364,7 @@
         <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>82</v>
@@ -6432,7 +6438,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>270</v>
@@ -6550,7 +6556,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>272</v>
@@ -6670,7 +6676,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>274</v>
@@ -6718,7 +6724,7 @@
         <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>82</v>
@@ -6757,7 +6763,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6781,7 +6787,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6792,10 +6798,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6821,13 +6827,13 @@
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6877,7 +6883,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6901,7 +6907,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6912,10 +6918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6941,14 +6947,14 @@
         <v>168</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6997,7 +7003,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7021,7 +7027,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7032,10 +7038,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7061,14 +7067,14 @@
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7117,7 +7123,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7141,7 +7147,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7152,10 +7158,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7178,19 +7184,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7239,7 +7245,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7263,7 +7269,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7274,10 +7280,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7303,16 +7309,16 @@
         <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7361,7 +7367,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7385,7 +7391,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7396,10 +7402,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7422,19 +7428,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7483,7 +7489,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7501,16 +7507,16 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7518,10 +7524,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7544,16 +7550,16 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7603,7 +7609,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7630,7 +7636,7 @@
         <v>253</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7638,14 +7644,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7664,19 +7670,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7725,7 +7731,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7743,16 +7749,16 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7760,14 +7766,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7786,19 +7792,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7847,7 +7853,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7862,19 +7868,19 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7882,10 +7888,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7911,13 +7917,13 @@
         <v>128</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7967,7 +7973,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7991,10 +7997,10 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8002,10 +8008,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8028,17 +8034,17 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8087,7 +8093,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8105,16 +8111,16 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8122,10 +8128,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8151,16 +8157,16 @@
         <v>235</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8189,7 +8195,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8207,7 +8213,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8216,7 +8222,7 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
@@ -8228,24 +8234,24 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8360,10 +8366,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8480,10 +8486,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8509,10 +8515,10 @@
         <v>146</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>261</v>
@@ -8602,10 +8608,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8720,10 +8726,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8840,10 +8846,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8927,7 +8933,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8951,7 +8957,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8962,10 +8968,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8991,13 +8997,13 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9047,7 +9053,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9071,7 +9077,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9082,10 +9088,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9111,14 +9117,14 @@
         <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9167,7 +9173,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9191,7 +9197,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9202,10 +9208,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9231,14 +9237,14 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9287,7 +9293,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9311,7 +9317,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9322,10 +9328,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9348,19 +9354,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9409,7 +9415,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9433,7 +9439,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9444,10 +9450,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9473,16 +9479,16 @@
         <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9531,7 +9537,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9555,7 +9561,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9566,10 +9572,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9595,16 +9601,16 @@
         <v>235</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9632,10 +9638,10 @@
         <v>150</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9653,7 +9659,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9662,7 +9668,7 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
@@ -9677,7 +9683,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9688,14 +9694,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9717,16 +9723,16 @@
         <v>235</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9754,10 +9760,10 @@
         <v>150</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9775,7 +9781,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9796,24 +9802,24 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9836,19 +9842,19 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9897,7 +9903,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9921,7 +9927,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9932,10 +9938,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9961,13 +9967,13 @@
         <v>235</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9996,10 +10002,10 @@
         <v>158</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10017,7 +10023,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10038,24 +10044,24 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10081,16 +10087,16 @@
         <v>235</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10118,10 +10124,10 @@
         <v>158</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10139,7 +10145,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10163,7 +10169,7 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10174,10 +10180,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10200,16 +10206,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10259,7 +10265,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10280,24 +10286,24 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10320,16 +10326,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10379,7 +10385,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10400,24 +10406,24 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10440,19 +10446,19 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10501,7 +10507,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10513,7 +10519,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10525,7 +10531,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10536,10 +10542,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10654,10 +10660,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10774,14 +10780,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10803,10 +10809,10 @@
         <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>116</v>
@@ -10861,7 +10867,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10896,10 +10902,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10922,13 +10928,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10979,7 +10985,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10988,7 +10994,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11003,7 +11009,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11014,10 +11020,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11040,13 +11046,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11097,7 +11103,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11106,7 +11112,7 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11121,7 +11127,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11132,10 +11138,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11161,16 +11167,16 @@
         <v>235</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11198,10 +11204,10 @@
         <v>172</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11219,7 +11225,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11240,10 +11246,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11254,10 +11260,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11283,16 +11289,16 @@
         <v>235</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11320,10 +11326,10 @@
         <v>158</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11341,7 +11347,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11362,10 +11368,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11376,10 +11382,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11402,17 +11408,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11461,7 +11467,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11496,10 +11502,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11525,10 +11531,10 @@
         <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11579,7 +11585,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11603,7 +11609,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11614,10 +11620,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11640,16 +11646,16 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11699,7 +11705,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11723,7 +11729,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11734,10 +11740,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11760,16 +11766,16 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11819,7 +11825,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11843,7 +11849,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -11854,10 +11860,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11880,19 +11886,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -11941,7 +11947,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11965,7 +11971,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -11976,10 +11982,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12094,10 +12100,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12214,14 +12220,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12243,10 +12249,10 @@
         <v>113</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>116</v>
@@ -12301,7 +12307,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12336,10 +12342,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12365,13 +12371,13 @@
         <v>235</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>248</v>
@@ -12423,7 +12429,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>93</v>
@@ -12444,7 +12450,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>253</v>
@@ -12458,10 +12464,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12484,19 +12490,19 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12545,7 +12551,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12566,24 +12572,24 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12609,16 +12615,16 @@
         <v>235</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12646,10 +12652,10 @@
         <v>150</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12667,7 +12673,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12676,7 +12682,7 @@
         <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>105</v>
@@ -12691,7 +12697,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12702,14 +12708,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12731,16 +12737,16 @@
         <v>235</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12768,10 +12774,10 @@
         <v>150</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12789,7 +12795,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12810,24 +12816,24 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12853,16 +12859,16 @@
         <v>83</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -12911,7 +12917,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12935,7 +12941,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-mii-pr-onko-prostate-gleason-score-gesamt.xlsx
+++ b/StructureDefinition-mii-pr-onko-prostate-gleason-score-gesamt.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:58:08+00:00</t>
+    <t>2026-09-15T07:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
